--- a/data/nzd0602/nzd0602.xlsx
+++ b/data/nzd0602/nzd0602.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M395"/>
+  <dimension ref="A1:M398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18223,6 +18223,141 @@
         <v>211.31</v>
       </c>
       <c r="M395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>206.97</v>
+      </c>
+      <c r="C396" t="n">
+        <v>194.93</v>
+      </c>
+      <c r="D396" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="E396" t="n">
+        <v>211.64</v>
+      </c>
+      <c r="F396" t="n">
+        <v>206.53</v>
+      </c>
+      <c r="G396" t="n">
+        <v>211.75</v>
+      </c>
+      <c r="H396" t="n">
+        <v>212.68</v>
+      </c>
+      <c r="I396" t="n">
+        <v>215.14</v>
+      </c>
+      <c r="J396" t="n">
+        <v>212.92</v>
+      </c>
+      <c r="K396" t="n">
+        <v>214.47</v>
+      </c>
+      <c r="L396" t="n">
+        <v>210.95</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>207.43</v>
+      </c>
+      <c r="C397" t="n">
+        <v>194.64</v>
+      </c>
+      <c r="D397" t="n">
+        <v>199.24</v>
+      </c>
+      <c r="E397" t="n">
+        <v>211.48</v>
+      </c>
+      <c r="F397" t="n">
+        <v>207.05</v>
+      </c>
+      <c r="G397" t="n">
+        <v>211.65</v>
+      </c>
+      <c r="H397" t="n">
+        <v>213.13</v>
+      </c>
+      <c r="I397" t="n">
+        <v>214.88</v>
+      </c>
+      <c r="J397" t="n">
+        <v>215.95</v>
+      </c>
+      <c r="K397" t="n">
+        <v>213.94</v>
+      </c>
+      <c r="L397" t="n">
+        <v>211.56</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>207.23</v>
+      </c>
+      <c r="C398" t="n">
+        <v>194.84</v>
+      </c>
+      <c r="D398" t="n">
+        <v>199.31</v>
+      </c>
+      <c r="E398" t="n">
+        <v>211.87</v>
+      </c>
+      <c r="F398" t="n">
+        <v>206.98</v>
+      </c>
+      <c r="G398" t="n">
+        <v>212.08</v>
+      </c>
+      <c r="H398" t="n">
+        <v>213</v>
+      </c>
+      <c r="I398" t="n">
+        <v>214.84</v>
+      </c>
+      <c r="J398" t="n">
+        <v>216</v>
+      </c>
+      <c r="K398" t="n">
+        <v>213.87</v>
+      </c>
+      <c r="L398" t="n">
+        <v>211</v>
+      </c>
+      <c r="M398" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18239,7 +18374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B425"/>
+  <dimension ref="A1:B428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22492,6 +22627,36 @@
       </c>
       <c r="B425" t="n">
         <v>-0.95</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -22654,28 +22819,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0007910315525574238</v>
+        <v>0.008107171970557138</v>
       </c>
       <c r="J2" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K2" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L2" t="n">
-        <v>2.062032528282742e-06</v>
+        <v>0.000216186627661652</v>
       </c>
       <c r="M2" t="n">
-        <v>3.285338672965852</v>
+        <v>3.304165750005803</v>
       </c>
       <c r="N2" t="n">
-        <v>15.89875739118731</v>
+        <v>16.04930093286361</v>
       </c>
       <c r="O2" t="n">
-        <v>3.987324590648134</v>
+        <v>4.006157876677305</v>
       </c>
       <c r="P2" t="n">
-        <v>201.1785069707892</v>
+        <v>201.0770412639539</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22726,28 +22891,28 @@
         <v>0.0982</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08301594495715149</v>
+        <v>0.091105150667909</v>
       </c>
       <c r="J3" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K3" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03321741468221928</v>
+        <v>0.03951307535879645</v>
       </c>
       <c r="M3" t="n">
-        <v>2.651561355095606</v>
+        <v>2.673061903846115</v>
       </c>
       <c r="N3" t="n">
-        <v>10.50891787405329</v>
+        <v>10.65311366821553</v>
       </c>
       <c r="O3" t="n">
-        <v>3.241746114990082</v>
+        <v>3.263910793544384</v>
       </c>
       <c r="P3" t="n">
-        <v>187.07724776185</v>
+        <v>186.985008675296</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22798,28 +22963,28 @@
         <v>0.0887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01291432864167832</v>
+        <v>0.02179917880050991</v>
       </c>
       <c r="J4" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K4" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007744878828106483</v>
+        <v>0.002184936172432206</v>
       </c>
       <c r="M4" t="n">
-        <v>2.663555750708623</v>
+        <v>2.690726536765476</v>
       </c>
       <c r="N4" t="n">
-        <v>11.27364955404819</v>
+        <v>11.4586022324942</v>
       </c>
       <c r="O4" t="n">
-        <v>3.357625582766516</v>
+        <v>3.385055720736986</v>
       </c>
       <c r="P4" t="n">
-        <v>193.0616836829045</v>
+        <v>192.9603751494944</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22870,28 +23035,28 @@
         <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02729822613377509</v>
+        <v>-0.02049324558168948</v>
       </c>
       <c r="J5" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K5" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002964617670169756</v>
+        <v>0.001678410979564338</v>
       </c>
       <c r="M5" t="n">
-        <v>2.917344578851496</v>
+        <v>2.934455331740367</v>
       </c>
       <c r="N5" t="n">
-        <v>13.13054365231313</v>
+        <v>13.18966348530186</v>
       </c>
       <c r="O5" t="n">
-        <v>3.623609202482123</v>
+        <v>3.631757630308203</v>
       </c>
       <c r="P5" t="n">
-        <v>207.7678648912513</v>
+        <v>207.6902668550297</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22942,28 +23107,28 @@
         <v>0.098</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1290491381088276</v>
+        <v>-0.1223082895912724</v>
       </c>
       <c r="J6" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K6" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04840171569093854</v>
+        <v>0.04395408152144586</v>
       </c>
       <c r="M6" t="n">
-        <v>3.129194355965867</v>
+        <v>3.139178114064288</v>
       </c>
       <c r="N6" t="n">
-        <v>17.15438238445726</v>
+        <v>17.18032611915233</v>
       </c>
       <c r="O6" t="n">
-        <v>4.141784927354058</v>
+        <v>4.144915695059711</v>
       </c>
       <c r="P6" t="n">
-        <v>205.7290401179331</v>
+        <v>205.6521726356053</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23014,28 +23179,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1479035550341156</v>
+        <v>-0.1378025420350796</v>
       </c>
       <c r="J7" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K7" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07501850616327188</v>
+        <v>0.06520839240157728</v>
       </c>
       <c r="M7" t="n">
-        <v>3.139739490234619</v>
+        <v>3.167045433314343</v>
       </c>
       <c r="N7" t="n">
-        <v>14.13168127205788</v>
+        <v>14.37360958796254</v>
       </c>
       <c r="O7" t="n">
-        <v>3.759212852720351</v>
+        <v>3.791254355482172</v>
       </c>
       <c r="P7" t="n">
-        <v>208.9246301118581</v>
+        <v>208.8094472837487</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23086,28 +23251,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06934970586175272</v>
+        <v>-0.06104171730984691</v>
       </c>
       <c r="J8" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K8" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02704483736522179</v>
+        <v>0.02086483610669421</v>
       </c>
       <c r="M8" t="n">
-        <v>2.439523464773703</v>
+        <v>2.462364110714757</v>
       </c>
       <c r="N8" t="n">
-        <v>9.065038969442904</v>
+        <v>9.232540722908686</v>
       </c>
       <c r="O8" t="n">
-        <v>3.010820315037565</v>
+        <v>3.038509621987182</v>
       </c>
       <c r="P8" t="n">
-        <v>209.1487851193439</v>
+        <v>209.0540489433953</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23158,28 +23323,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.261971771754318</v>
+        <v>0.2686468317403332</v>
       </c>
       <c r="J9" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K9" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2182841448147615</v>
+        <v>0.2276053540955258</v>
       </c>
       <c r="M9" t="n">
-        <v>2.802097368709049</v>
+        <v>2.814325961469517</v>
       </c>
       <c r="N9" t="n">
-        <v>12.87679256231075</v>
+        <v>12.93183939037235</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58842480237649</v>
+        <v>3.596086677260762</v>
       </c>
       <c r="P9" t="n">
-        <v>203.3914504736196</v>
+        <v>203.3153386253176</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23230,28 +23395,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3668059352059712</v>
+        <v>0.3693905817283908</v>
       </c>
       <c r="J10" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K10" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4262134312051129</v>
+        <v>0.4324193630670302</v>
       </c>
       <c r="M10" t="n">
-        <v>2.557142801941879</v>
+        <v>2.553708610035519</v>
       </c>
       <c r="N10" t="n">
-        <v>9.490037554937489</v>
+        <v>9.456581064595325</v>
       </c>
       <c r="O10" t="n">
-        <v>3.080590455568135</v>
+        <v>3.075155453728368</v>
       </c>
       <c r="P10" t="n">
-        <v>203.3648982319077</v>
+        <v>203.3354041746623</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23302,28 +23467,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4050853944091348</v>
+        <v>0.4056429241530926</v>
       </c>
       <c r="J11" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K11" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5428562853782513</v>
+        <v>0.5472854591847156</v>
       </c>
       <c r="M11" t="n">
-        <v>2.025293849771733</v>
+        <v>2.012571832477</v>
       </c>
       <c r="N11" t="n">
-        <v>7.23990766950026</v>
+        <v>7.186847327712263</v>
       </c>
       <c r="O11" t="n">
-        <v>2.690707652180047</v>
+        <v>2.680829596918137</v>
       </c>
       <c r="P11" t="n">
-        <v>202.8507771780187</v>
+        <v>202.8444244810741</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23374,28 +23539,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.337319351053137</v>
+        <v>0.3352370519178858</v>
       </c>
       <c r="J12" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K12" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3922728137241513</v>
+        <v>0.39257758737765</v>
       </c>
       <c r="M12" t="n">
-        <v>2.329038078955157</v>
+        <v>2.320323479185408</v>
       </c>
       <c r="N12" t="n">
-        <v>9.235808984832998</v>
+        <v>9.181410637778495</v>
       </c>
       <c r="O12" t="n">
-        <v>3.039047381143143</v>
+        <v>3.030084262488173</v>
       </c>
       <c r="P12" t="n">
-        <v>203.5390829799525</v>
+        <v>203.5628278271942</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23433,7 +23598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M395"/>
+  <dimension ref="A1:M398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49901,6 +50066,207 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-36.878971912529785,175.04225529001857</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-36.87951876279781,175.04285538373725</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-36.879948942846966,175.0435774947905</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-36.880271367619116,175.04435883870823</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-36.88062445618212,175.04514325306027</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-36.88081901250846,175.04598227388666</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-36.880982785529305,175.0468560980835</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-36.88101879673654,175.04772060336077</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-36.88106953650621,175.0486160729035</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-36.881031454298764,175.0494981748884</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-36.88099197480037,175.0503743627298</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-36.87896873889405,175.04225860901326</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-36.87952076357852,175.0428532913293</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-36.87995280644733,175.04357345429443</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-36.88027266757162,175.04435806256544</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-36.88062023132102,175.04514577549085</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-36.880819887475724,175.04598200574947</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-36.88097884729891,175.04685730024875</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-36.881021137423,175.04772047842624</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-36.881042258505396,175.04861752855183</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>-36.88103622424973,175.04949846852423</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>-36.88098657216094,175.05037310266388</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-36.8789701187357,175.04225716597213</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-36.87951938372976,175.04285473436929</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-36.8799523234973,175.04357395935648</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-36.8802694989374,175.04435995441347</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-36.88062080005232,175.0451454359329</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-36.88081612511649,175.04598315873938</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-36.880979985009915,175.04685695295657</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-36.8810214975286,175.04772045920555</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-36.88104180837337,175.04861755257244</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>-36.88103685424325,175.0494985073063</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>-36.88099153196107,175.0503742594457</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0602/nzd0602.xlsx
+++ b/data/nzd0602/nzd0602.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M398"/>
+  <dimension ref="A1:M400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18358,6 +18358,96 @@
         <v>211</v>
       </c>
       <c r="M398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>207.72</v>
+      </c>
+      <c r="C399" t="n">
+        <v>194.91</v>
+      </c>
+      <c r="D399" t="n">
+        <v>200.14</v>
+      </c>
+      <c r="E399" t="n">
+        <v>212.2</v>
+      </c>
+      <c r="F399" t="n">
+        <v>207.65</v>
+      </c>
+      <c r="G399" t="n">
+        <v>212.59</v>
+      </c>
+      <c r="H399" t="n">
+        <v>213.28</v>
+      </c>
+      <c r="I399" t="n">
+        <v>215</v>
+      </c>
+      <c r="J399" t="n">
+        <v>216.28</v>
+      </c>
+      <c r="K399" t="n">
+        <v>213.96</v>
+      </c>
+      <c r="L399" t="n">
+        <v>210.94</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>207.28</v>
+      </c>
+      <c r="C400" t="n">
+        <v>193.91</v>
+      </c>
+      <c r="D400" t="n">
+        <v>198.66</v>
+      </c>
+      <c r="E400" t="n">
+        <v>211.67</v>
+      </c>
+      <c r="F400" t="n">
+        <v>206.41</v>
+      </c>
+      <c r="G400" t="n">
+        <v>211.95</v>
+      </c>
+      <c r="H400" t="n">
+        <v>213.07</v>
+      </c>
+      <c r="I400" t="n">
+        <v>215.11</v>
+      </c>
+      <c r="J400" t="n">
+        <v>216.09</v>
+      </c>
+      <c r="K400" t="n">
+        <v>214.11</v>
+      </c>
+      <c r="L400" t="n">
+        <v>210.49</v>
+      </c>
+      <c r="M400" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18374,7 +18464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B428"/>
+  <dimension ref="A1:B430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22657,6 +22747,26 @@
       </c>
       <c r="B428" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -22819,28 +22929,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008107171970557138</v>
+        <v>0.01415116246246496</v>
       </c>
       <c r="J2" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000216186627661652</v>
+        <v>0.000657270684523259</v>
       </c>
       <c r="M2" t="n">
-        <v>3.304165750005803</v>
+        <v>3.318106007424438</v>
       </c>
       <c r="N2" t="n">
-        <v>16.04930093286361</v>
+        <v>16.15919822952458</v>
       </c>
       <c r="O2" t="n">
-        <v>4.006157876677305</v>
+        <v>4.019850523281256</v>
       </c>
       <c r="P2" t="n">
-        <v>201.0770412639539</v>
+        <v>201.007853084502</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22891,28 +23001,28 @@
         <v>0.0982</v>
       </c>
       <c r="I3" t="n">
-        <v>0.091105150667909</v>
+        <v>0.09594932192113712</v>
       </c>
       <c r="J3" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K3" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03951307535879645</v>
+        <v>0.04357886798553035</v>
       </c>
       <c r="M3" t="n">
-        <v>2.673061903846115</v>
+        <v>2.68495908338351</v>
       </c>
       <c r="N3" t="n">
-        <v>10.65311366821553</v>
+        <v>10.72315091894164</v>
       </c>
       <c r="O3" t="n">
-        <v>3.263910793544384</v>
+        <v>3.27462225591619</v>
       </c>
       <c r="P3" t="n">
-        <v>186.985008675296</v>
+        <v>186.9295605533888</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22963,28 +23073,28 @@
         <v>0.0887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02179917880050991</v>
+        <v>0.02749906118398675</v>
       </c>
       <c r="J4" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K4" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002184936172432206</v>
+        <v>0.003455806291434715</v>
       </c>
       <c r="M4" t="n">
-        <v>2.690726536765476</v>
+        <v>2.707729271742647</v>
       </c>
       <c r="N4" t="n">
-        <v>11.4586022324942</v>
+        <v>11.57306218732067</v>
       </c>
       <c r="O4" t="n">
-        <v>3.385055720736986</v>
+        <v>3.401920367574861</v>
       </c>
       <c r="P4" t="n">
-        <v>192.9603751494944</v>
+        <v>192.8951345797672</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23035,28 +23145,28 @@
         <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02049324558168948</v>
+        <v>-0.01582321932123944</v>
       </c>
       <c r="J5" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001678410979564338</v>
+        <v>0.001002804958813996</v>
       </c>
       <c r="M5" t="n">
-        <v>2.934455331740367</v>
+        <v>2.946611267720281</v>
       </c>
       <c r="N5" t="n">
-        <v>13.18966348530186</v>
+        <v>13.23740546241293</v>
       </c>
       <c r="O5" t="n">
-        <v>3.631757630308203</v>
+        <v>3.638324540556124</v>
       </c>
       <c r="P5" t="n">
-        <v>207.6902668550297</v>
+        <v>207.6368085177251</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23107,28 +23217,28 @@
         <v>0.098</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1223082895912724</v>
+        <v>-0.1177630030953783</v>
       </c>
       <c r="J6" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K6" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04395408152144586</v>
+        <v>0.0410268296492704</v>
       </c>
       <c r="M6" t="n">
-        <v>3.139178114064288</v>
+        <v>3.146674597855275</v>
       </c>
       <c r="N6" t="n">
-        <v>17.18032611915233</v>
+        <v>17.20369058865494</v>
       </c>
       <c r="O6" t="n">
-        <v>4.144915695059711</v>
+        <v>4.147733186772618</v>
       </c>
       <c r="P6" t="n">
-        <v>205.6521726356053</v>
+        <v>205.6001479566458</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23179,28 +23289,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1378025420350796</v>
+        <v>-0.1308200678500537</v>
       </c>
       <c r="J7" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K7" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06520839240157728</v>
+        <v>0.0587341335823478</v>
       </c>
       <c r="M7" t="n">
-        <v>3.167045433314343</v>
+        <v>3.186670880041727</v>
       </c>
       <c r="N7" t="n">
-        <v>14.37360958796254</v>
+        <v>14.55579275315502</v>
       </c>
       <c r="O7" t="n">
-        <v>3.791254355482172</v>
+        <v>3.815205466702287</v>
       </c>
       <c r="P7" t="n">
-        <v>208.8094472837487</v>
+        <v>208.7295168337097</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23251,28 +23361,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06104171730984691</v>
+        <v>-0.05542938238759457</v>
       </c>
       <c r="J8" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K8" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02086483610669421</v>
+        <v>0.01714018663532724</v>
       </c>
       <c r="M8" t="n">
-        <v>2.462364110714757</v>
+        <v>2.478003899606476</v>
       </c>
       <c r="N8" t="n">
-        <v>9.232540722908686</v>
+        <v>9.350212710440031</v>
       </c>
       <c r="O8" t="n">
-        <v>3.038509621987182</v>
+        <v>3.057811751962509</v>
       </c>
       <c r="P8" t="n">
-        <v>209.0540489433953</v>
+        <v>208.9898004722041</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23323,28 +23433,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2686468317403332</v>
+        <v>0.273043822717067</v>
       </c>
       <c r="J9" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K9" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2276053540955258</v>
+        <v>0.2337867052123118</v>
       </c>
       <c r="M9" t="n">
-        <v>2.814325961469517</v>
+        <v>2.822495288044279</v>
       </c>
       <c r="N9" t="n">
-        <v>12.93183939037235</v>
+        <v>12.96761069946499</v>
       </c>
       <c r="O9" t="n">
-        <v>3.596086677260762</v>
+        <v>3.601056886452224</v>
       </c>
       <c r="P9" t="n">
-        <v>203.3153386253176</v>
+        <v>203.2650010608221</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23395,28 +23505,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3693905817283908</v>
+        <v>0.3722233168665387</v>
       </c>
       <c r="J10" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K10" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4324193630670302</v>
+        <v>0.4375789118449024</v>
       </c>
       <c r="M10" t="n">
-        <v>2.553708610035519</v>
+        <v>2.556746036025514</v>
       </c>
       <c r="N10" t="n">
-        <v>9.456581064595325</v>
+        <v>9.450999538668821</v>
       </c>
       <c r="O10" t="n">
-        <v>3.075155453728368</v>
+        <v>3.074247800465802</v>
       </c>
       <c r="P10" t="n">
-        <v>203.3354041746623</v>
+        <v>203.3029767295403</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23467,28 +23577,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4056429241530926</v>
+        <v>0.4059078812531253</v>
       </c>
       <c r="J11" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K11" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5472854591847156</v>
+        <v>0.5501087463742755</v>
       </c>
       <c r="M11" t="n">
-        <v>2.012571832477</v>
+        <v>2.003689941257631</v>
       </c>
       <c r="N11" t="n">
-        <v>7.186847327712263</v>
+        <v>7.151206973166826</v>
       </c>
       <c r="O11" t="n">
-        <v>2.680829596918137</v>
+        <v>2.674174073086273</v>
       </c>
       <c r="P11" t="n">
-        <v>202.8444244810741</v>
+        <v>202.8413902588423</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23539,28 +23649,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3352370519178858</v>
+        <v>0.3334158446450215</v>
       </c>
       <c r="J12" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K12" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L12" t="n">
-        <v>0.39257758737765</v>
+        <v>0.3919428259849225</v>
       </c>
       <c r="M12" t="n">
-        <v>2.320323479185408</v>
+        <v>2.316346215877082</v>
       </c>
       <c r="N12" t="n">
-        <v>9.181410637778495</v>
+        <v>9.152917468099766</v>
       </c>
       <c r="O12" t="n">
-        <v>3.030084262488173</v>
+        <v>3.025378896617706</v>
       </c>
       <c r="P12" t="n">
-        <v>203.5628278271942</v>
+        <v>203.5836808556114</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23598,7 +23708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M398"/>
+  <dimension ref="A1:M400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50267,6 +50377,140 @@
         </is>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>-36.878966738123644,175.04226070142283</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>-36.87951890078269,175.04285523943324</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>-36.87994659708953,175.04357994794861</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-36.88026681778534,175.04436155520781</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>-36.88061535648121,175.04514868598733</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-36.88081166278344,175.0459845262389</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-36.880977534555434,175.0468577009705</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-36.88102005710616,175.04772053608835</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>-36.88103928763401,175.04861768708778</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>-36.88103604425158,175.04949845744363</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>-36.880992063368225,175.05037438338664</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-36.87896977377528,175.0422575267324</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-36.87952580002631,175.042848024233</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-36.87995680803329,175.04356926949453</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-36.88027112387803,175.04435898423503</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-36.88062543115008,175.0451426709609</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-36.88081726257393,175.04598281016106</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-36.8809793723963,175.04685713996008</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-36.88101906681575,175.04772058894525</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-36.881040998135724,175.04861759580953</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>-36.88103469426546,175.04949837433915</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>-36.88099604892189,175.0503753129436</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
